--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -22321,12 +22321,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22351,12 +22351,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N126" t="n">
@@ -22399,40 +22399,185 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW126" t="inlineStr">
+      <c r="AW127" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
+      <c r="AX127" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY126" t="inlineStr">
+      <c r="AY127" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
+      <c r="AZ127" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA126" t="inlineStr">
+      <c r="BA127" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB126" t="inlineStr">
+      <c r="BB127" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC126" t="inlineStr">
+      <c r="BC127" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -22554,7 +22699,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -22564,7 +22709,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -20020,12 +20020,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20062,6 +20062,9 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
@@ -20098,42 +20101,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20165,12 +20168,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20195,7 +20198,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20243,42 +20246,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20310,12 +20313,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20354,9 +20357,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20365,77 +20365,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20462,7 +20453,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -20514,98 +20505,18 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -20699,17 +20610,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20734,7 +20645,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20748,76 +20659,168 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -20849,12 +20852,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20893,9 +20896,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20904,77 +20904,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21001,7 +20992,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -21053,98 +21044,18 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -21238,17 +21149,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21273,7 +21184,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21287,76 +21198,168 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21388,12 +21391,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21432,9 +21435,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -21443,77 +21443,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21540,7 +21531,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -21592,98 +21583,18 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -21777,17 +21688,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21812,7 +21723,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21826,76 +21737,168 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21927,12 +21930,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21971,9 +21974,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21982,77 +21982,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22079,7 +22070,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -22131,98 +22122,18 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -22316,17 +22227,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22351,7 +22262,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22365,76 +22276,168 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22466,12 +22469,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22496,12 +22499,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -22544,40 +22547,579 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW127" t="inlineStr">
+      <c r="AW130" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
+      <c r="AX130" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY127" t="inlineStr">
+      <c r="AY130" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
+      <c r="AZ130" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA127" t="inlineStr">
+      <c r="BA130" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB127" t="inlineStr">
+      <c r="BB130" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC127" t="inlineStr">
+      <c r="BC130" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -22699,7 +23241,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -22709,7 +23251,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -22729,7 +23271,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -23125,6 +23125,151 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23158,7 +23303,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -23241,7 +23386,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -23251,7 +23396,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -23270,6 +23270,400 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23386,7 +23780,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -23396,7 +23790,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -23416,7 +23810,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -20168,12 +20168,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20246,42 +20246,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20313,12 +20313,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20391,42 +20391,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20458,12 +20458,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20502,9 +20502,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -20513,77 +20510,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20598,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -20662,98 +20650,18 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -20847,17 +20755,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20882,7 +20790,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20896,76 +20804,168 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -20997,12 +20997,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21041,9 +21041,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21052,77 +21049,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21149,7 +21137,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21201,98 +21189,18 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -21386,17 +21294,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21421,7 +21329,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21435,76 +21343,168 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21536,12 +21536,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21580,9 +21580,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21591,77 +21588,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21688,7 +21676,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -21740,98 +21728,18 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -21925,17 +21833,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21960,7 +21868,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21974,76 +21882,168 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22075,12 +22075,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22119,9 +22119,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22130,77 +22127,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22227,7 +22215,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22279,98 +22267,18 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -22464,17 +22372,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22499,7 +22407,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22513,76 +22421,168 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22614,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22658,9 +22658,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22669,77 +22666,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22766,7 +22754,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -22818,98 +22806,18 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -23003,17 +22911,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -23038,12 +22946,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -23052,76 +22960,168 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -23153,12 +23153,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -23231,42 +23231,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23298,12 +23298,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23342,9 +23342,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23353,77 +23350,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23450,7 +23438,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -23502,98 +23490,18 @@
       <c r="P133" t="n">
         <v>0</v>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SARS</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN133" t="b">
-        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -23659,6 +23567,782 @@
         </is>
       </c>
       <c r="BC133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -23697,7 +24381,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -23780,7 +24464,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -23790,7 +24474,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -23810,7 +24494,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -35268,6 +35268,690 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35301,7 +35985,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -35384,7 +36068,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -35394,7 +36078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -35414,7 +36098,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -35835,12 +35835,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35865,12 +35865,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -35913,40 +35913,185 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
+      <c r="AT198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW197" t="inlineStr">
+      <c r="AW198" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX197" t="inlineStr">
+      <c r="AX198" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr">
+      <c r="AY198" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ197" t="inlineStr">
+      <c r="AZ198" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA197" t="inlineStr">
+      <c r="BA198" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB197" t="inlineStr">
+      <c r="BB198" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC197" t="inlineStr">
+      <c r="BC198" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -36068,7 +36213,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -36078,7 +36223,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1311,6 +1316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1456,6 +1466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3772,6 +3787,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4307,6 +4327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4452,6 +4477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6768,6 +6798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6913,6 +6948,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7058,6 +7098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9768,6 +9813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9913,6 +9963,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10058,6 +10113,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12374,6 +12434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13299,6 +13364,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13444,6 +13514,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16302,6 +16377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19567,6 +19647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19712,6 +19797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22016,6 +22106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25671,6 +25766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25816,6 +25916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28265,6 +28370,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31140,6 +31250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31285,6 +31400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34125,6 +34245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35980,118 +36105,517 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>SARS</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
         <is>
           <t>传染性非典型肺炎</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N198" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" t="n">
-        <v>0</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr">
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO198" t="inlineStr">
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP198" t="inlineStr">
+      <c r="AP200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR198" t="inlineStr">
+      <c r="AR200" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS198" t="inlineStr"/>
-      <c r="AT198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV198" t="inlineStr">
+      <c r="AV200" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW198" t="inlineStr">
+      <c r="AW200" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX198" t="inlineStr">
+      <c r="AX200" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY198" t="inlineStr">
+      <c r="AY200" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ198" t="inlineStr">
+      <c r="AZ200" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA198" t="inlineStr">
+      <c r="BA200" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB198" t="inlineStr">
+      <c r="BB200" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC198" t="inlineStr">
+      <c r="BC200" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -36213,7 +36737,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -36223,7 +36747,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -36243,7 +36767,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -36621,6 +36621,151 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36654,7 +36799,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -36747,7 +36892,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d003/2026-2029.xlsx
+++ b/diseases/d003/2026-2029.xlsx
@@ -36766,6 +36766,400 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SARS; SER_SG_HIST_SARS</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36882,7 +37276,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -36892,7 +37286,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -36912,7 +37306,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
